--- a/output/roomself_excel/8572.xlsx
+++ b/output/roomself_excel/8572.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>410861</v>
+        <v>59171</v>
       </c>
       <c r="D2" t="n">
-        <v>7764</v>
+        <v>2020</v>
       </c>
       <c r="E2" t="n">
-        <v>986</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>719</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>78249</v>
+        <v>264248</v>
       </c>
       <c r="D3" t="n">
-        <v>2876</v>
+        <v>5156</v>
       </c>
       <c r="E3" t="n">
-        <v>230</v>
+        <v>707</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19030</v>
+        <v>108532</v>
       </c>
       <c r="D5" t="n">
-        <v>1132</v>
+        <v>2844</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17480</v>
+        <v>72750</v>
       </c>
       <c r="D6" t="n">
-        <v>1068</v>
+        <v>2164</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -576,14 +576,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9890</v>
+        <v>21538</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>1192</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>108532</v>
+        <v>19030</v>
       </c>
       <c r="D8" t="n">
-        <v>2844</v>
+        <v>1132</v>
       </c>
       <c r="E8" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>72750</v>
+        <v>17480</v>
       </c>
       <c r="D9" t="n">
-        <v>2164</v>
+        <v>1068</v>
       </c>
       <c r="E9" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,19 +642,85 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>87442</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E10" t="n">
+        <v>164</v>
+      </c>
+      <c r="F10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>9890</v>
+      </c>
+      <c r="D11" t="n">
+        <v>804</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C12" t="n">
+        <v>56711</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E12" t="n">
+        <v>230</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>52008</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D13" t="n">
         <v>1844</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E13" t="n">
         <v>197</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F13" t="n">
         <v>16</v>
       </c>
     </row>

--- a/output/roomself_excel/8572.xlsx
+++ b/output/roomself_excel/8572.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,12 @@
       <c r="D2" t="n">
         <v>2020</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +517,27 @@
       <c r="D3" t="n">
         <v>5156</v>
       </c>
-      <c r="E3" t="n">
-        <v>707</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>372</v>
+        <v>691</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>356</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +555,20 @@
       <c r="D4" t="n">
         <v>2244</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>213</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>16</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +585,27 @@
       <c r="D5" t="n">
         <v>2844</v>
       </c>
-      <c r="E5" t="n">
-        <v>379</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>300</v>
+        <v>363</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>284</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +623,26 @@
       <c r="D6" t="n">
         <v>2164</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>291</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>250</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>16</v>
       </c>
     </row>
@@ -585,12 +661,20 @@
       <c r="D7" t="n">
         <v>1192</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +691,20 @@
       <c r="D8" t="n">
         <v>1132</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +721,12 @@
       <c r="D9" t="n">
         <v>1068</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +743,20 @@
       <c r="D10" t="n">
         <v>2892</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>164</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>16</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +773,20 @@
       <c r="D11" t="n">
         <v>804</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +803,27 @@
       <c r="D12" t="n">
         <v>2028</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>230</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>266</v>
+      </c>
+      <c r="J12" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +841,20 @@
       <c r="D13" t="n">
         <v>1844</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>197</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>16</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
